--- a/CWE_Examples/CWE-226/CWE-226-vulnerability-mapping.xlsx
+++ b/CWE_Examples/CWE-226/CWE-226-vulnerability-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\parks\OneDrive\Documents\UC\Research\DetectRTL\CWE_Examples\CWE-226\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D783390-1AB2-41E8-B985-4500CAFCC605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D94F2E-50C9-4E41-93D8-E75B11FCC00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19125" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9690" yWindow="-16455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -498,13 +498,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,12 +541,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2875C424-162A-465F-BE18-E16889C888B0}" name="Table1" displayName="Table1" ref="A2:C76" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2875C424-162A-465F-BE18-E16889C888B0}" name="Table1" displayName="Table1" ref="A2:C76" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A2:C76" xr:uid="{2875C424-162A-465F-BE18-E16889C888B0}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9F4319D7-1635-4A81-A0F8-EBA136083169}" name="File Name" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{C43F72EB-39E4-4FEB-9815-C112CF297539}" name="Register" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{85079F56-2EB8-49BD-ACE4-89108FC635A3}" name="Reset Coverage" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{9F4319D7-1635-4A81-A0F8-EBA136083169}" name="File Name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{C43F72EB-39E4-4FEB-9815-C112CF297539}" name="Register" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{85079F56-2EB8-49BD-ACE4-89108FC635A3}" name="Reset Coverage" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -829,11 +829,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -847,13 +847,13 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -867,13 +867,13 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -887,13 +887,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -907,13 +907,13 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -927,13 +927,13 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -947,13 +947,13 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -967,13 +967,13 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -987,13 +987,13 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1007,13 +1007,13 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1027,13 +1027,13 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1047,13 +1047,13 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1067,365 +1067,373 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="F14" s="1">
+        <f>SUM(F4:F13)</f>
+        <v>82</v>
+      </c>
+      <c r="G14" s="1">
+        <f>SUM(G4:G13)</f>
+        <v>32</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1441,321 +1449,321 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="3" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>21</v>
       </c>
     </row>
